--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_36.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1857009.79870476</v>
+        <v>1849002.956897863</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7069717.394383962</v>
+        <v>7069717.394383961</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7069717.394383962</v>
+        <v>7069717.394383961</v>
       </c>
     </row>
     <row r="9">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>124.847876179682</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>124.847876179682</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>168.4149913854146</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>210.6156651633976</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -973,22 +973,22 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>175.4172848236332</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>199.8180013219742</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1146,10 +1146,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>26.34349040625725</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>398.2660155522383</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,22 +1255,22 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>421</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>11.13051634550924</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>138.7932038659039</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1368,7 +1368,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>229.9677708001137</v>
       </c>
       <c r="D11" t="n">
         <v>185.3391557398498</v>
@@ -1383,7 +1383,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>188.5028512606473</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>344.5479255901462</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>179.3632896068686</v>
+        <v>184.8564821639885</v>
       </c>
       <c r="F14" t="n">
         <v>179.8896287080119</v>
@@ -1623,7 +1623,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>340.7767994885277</v>
+        <v>227.8260302548208</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S17" t="n">
         <v>269.8481678023229</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>294.4243626791926</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>256.9993129555745</v>
+        <v>262.4925055126944</v>
       </c>
       <c r="C20" t="n">
         <v>224.4745782429939</v>
@@ -2097,7 +2097,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2279,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>345.9207354288559</v>
       </c>
       <c r="R22" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>185.3391557398498</v>
+        <v>190.8323482969696</v>
       </c>
       <c r="E23" t="n">
         <v>179.3632896068686</v>
@@ -2382,7 +2382,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>291.8106252399262</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="24">
@@ -2477,19 +2477,19 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2.642208012909668</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>233.3594533926489</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>429.7144891057306</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
         <v>404.8510241668239</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2750,10 +2750,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>83.53494458290474</v>
       </c>
       <c r="Q28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -2838,7 +2838,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>275.3413603594427</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
@@ -2856,7 +2856,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>286.3174326828064</v>
+        <v>291.8106252399262</v>
       </c>
     </row>
     <row r="30">
@@ -2987,13 +2987,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>279.684256477775</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -3036,7 +3036,7 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>179.8896287080119</v>
+        <v>185.3828212651317</v>
       </c>
       <c r="G32" t="n">
         <v>178.7573722870162</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S32" t="n">
         <v>269.8481678023229</v>
@@ -3194,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>296.537879461114</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3391,10 +3391,10 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S36" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T36" t="n">
-        <v>118.0355277429562</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
         <v>50.21035976018675</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X38" t="n">
         <v>242.2818334606677</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>91.60958778454074</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900538</v>
       </c>
       <c r="T39" t="n">
         <v>55.35776521751382</v>
@@ -3753,10 +3753,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>73.77767497096178</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3871,10 +3871,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U42" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>82.37314290982852</v>
@@ -4102,13 +4102,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900538</v>
       </c>
       <c r="T45" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
         <v>64.51066719152016</v>
@@ -4120,7 +4120,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4333,13 +4333,13 @@
         <v>841.7791130376559</v>
       </c>
       <c r="N2" t="n">
-        <v>1258.569113037656</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1675.359113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1684</v>
+        <v>1267.21</v>
       </c>
       <c r="Q2" t="n">
         <v>1684</v>
@@ -4382,16 +4382,16 @@
         <v>725.2419790837811</v>
       </c>
       <c r="D3" t="n">
-        <v>725.2419790837811</v>
+        <v>599.1330132457184</v>
       </c>
       <c r="E3" t="n">
-        <v>379.1085475464956</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>379.1085475464956</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>379.1085475464956</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="H3" t="n">
         <v>252.9995817084329</v>
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>892.1583371018271</v>
+        <v>640.1977900567689</v>
       </c>
       <c r="C4" t="n">
-        <v>1018.160342920263</v>
+        <v>640.1977900567689</v>
       </c>
       <c r="D4" t="n">
-        <v>1131.479487045263</v>
+        <v>640.1977900567689</v>
       </c>
       <c r="E4" t="n">
-        <v>1249.308391256676</v>
+        <v>698.4996236645361</v>
       </c>
       <c r="F4" t="n">
-        <v>1373.669363848611</v>
+        <v>698.4996236645361</v>
       </c>
       <c r="G4" t="n">
-        <v>1527.075929735497</v>
+        <v>851.9061895514213</v>
       </c>
       <c r="H4" t="n">
-        <v>1527.075929735497</v>
+        <v>851.9061895514213</v>
       </c>
       <c r="I4" t="n">
-        <v>1544.487243076824</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="J4" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T4" t="n">
-        <v>259.005934252978</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>259.005934252978</v>
+        <v>468.3068717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>457.8273271389239</v>
+        <v>468.3068717970915</v>
       </c>
       <c r="W4" t="n">
-        <v>629.7182453986013</v>
+        <v>640.1977900567689</v>
       </c>
       <c r="X4" t="n">
-        <v>780.7490364227948</v>
+        <v>640.1977900567689</v>
       </c>
       <c r="Y4" t="n">
-        <v>892.1583371018271</v>
+        <v>640.1977900567689</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266.9273161322752</v>
+        <v>115.3301851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>216.9529946747056</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>206.5094030182917</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E5" t="n">
-        <v>202.1020397790304</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>197.1630208820488</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G5" t="n">
-        <v>193.3676953396081</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H5" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I5" t="n">
         <v>33.68</v>
@@ -4567,43 +4567,43 @@
         <v>867.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1267.21</v>
+        <v>867.2600000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>1267.21</v>
+        <v>1284.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1267.21</v>
+        <v>1284.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1267.21</v>
+        <v>1284.05</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
       </c>
       <c r="R5" t="n">
-        <v>1684</v>
+        <v>1513.88384708544</v>
       </c>
       <c r="S5" t="n">
-        <v>1588.193769896644</v>
+        <v>1418.077616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1399.632576231427</v>
+        <v>1229.516423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1147.893892848992</v>
+        <v>977.7777399344324</v>
       </c>
       <c r="V5" t="n">
-        <v>915.7211411653319</v>
+        <v>745.6049882507718</v>
       </c>
       <c r="W5" t="n">
-        <v>674.9398522956878</v>
+        <v>504.8236993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>462.1967561710438</v>
+        <v>310.5996251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>349.7549049762899</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4616,19 +4616,19 @@
         <v>900.0695195792149</v>
       </c>
       <c r="C6" t="n">
-        <v>900.0695195792149</v>
+        <v>722.8803429896864</v>
       </c>
       <c r="D6" t="n">
-        <v>900.0695195792149</v>
+        <v>722.8803429896864</v>
       </c>
       <c r="E6" t="n">
-        <v>900.0695195792149</v>
+        <v>376.7469114524009</v>
       </c>
       <c r="F6" t="n">
-        <v>698.2331546075238</v>
+        <v>33.68</v>
       </c>
       <c r="G6" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="H6" t="n">
         <v>33.68</v>
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>407.8774293695179</v>
+        <v>687.9643241161262</v>
       </c>
       <c r="C7" t="n">
-        <v>533.8794351879537</v>
+        <v>687.9643241161262</v>
       </c>
       <c r="D7" t="n">
-        <v>647.1985793129538</v>
+        <v>801.2834682411263</v>
       </c>
       <c r="E7" t="n">
-        <v>765.0274835243669</v>
+        <v>919.1123724525394</v>
       </c>
       <c r="F7" t="n">
-        <v>889.3884561163023</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="G7" t="n">
-        <v>1042.795022003188</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="H7" t="n">
-        <v>1212.311607162585</v>
+        <v>1212.989930203873</v>
       </c>
       <c r="I7" t="n">
-        <v>1433.444486098668</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J7" t="n">
         <v>1434.122809139956</v>
@@ -4743,25 +4743,25 @@
         <v>33.68</v>
       </c>
       <c r="S7" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>33.68</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>33.68</v>
+        <v>259.005934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>33.68</v>
+        <v>404.3160681901568</v>
       </c>
       <c r="W7" t="n">
-        <v>33.68</v>
+        <v>576.2069864498342</v>
       </c>
       <c r="X7" t="n">
-        <v>184.7107910241935</v>
+        <v>576.2069864498342</v>
       </c>
       <c r="Y7" t="n">
-        <v>296.1200917032258</v>
+        <v>576.2069864498342</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>285.4463380542246</v>
+        <v>115.3301851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>235.472016596655</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E8" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>215.6820428039981</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G8" t="n">
-        <v>211.8867172615575</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I8" t="n">
         <v>33.68</v>
       </c>
       <c r="J8" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="K8" t="n">
-        <v>33.68</v>
+        <v>841.7791130376557</v>
       </c>
       <c r="L8" t="n">
-        <v>33.68</v>
+        <v>841.7791130376557</v>
       </c>
       <c r="M8" t="n">
-        <v>450.47</v>
+        <v>841.7791130376557</v>
       </c>
       <c r="N8" t="n">
-        <v>867.26</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="O8" t="n">
-        <v>1284.05</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="P8" t="n">
-        <v>1284.05</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="Q8" t="n">
         <v>1684</v>
@@ -4831,16 +4831,16 @@
         <v>1147.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>915.7211411653319</v>
+        <v>745.6049882507718</v>
       </c>
       <c r="W8" t="n">
-        <v>674.9398522956878</v>
+        <v>504.8236993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>480.7157780929932</v>
+        <v>310.5996251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>368.2739268982392</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.68</v>
+        <v>617.7469680170383</v>
       </c>
       <c r="C9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="D9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="E9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="F9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="G9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="H9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="I9" t="n">
         <v>33.68</v>
@@ -4898,28 +4898,28 @@
         <v>1014.284879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>589.0323546205764</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S9" t="n">
-        <v>521.7959910199589</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T9" t="n">
-        <v>112.3437029214601</v>
+        <v>792.8752208079458</v>
       </c>
       <c r="U9" t="n">
-        <v>101.1007571179154</v>
+        <v>792.6627362016965</v>
       </c>
       <c r="V9" t="n">
-        <v>86.44351753052129</v>
+        <v>778.0054966143024</v>
       </c>
       <c r="W9" t="n">
-        <v>53.74337317715914</v>
+        <v>637.8103411941975</v>
       </c>
       <c r="X9" t="n">
-        <v>33.68</v>
+        <v>617.7469680170383</v>
       </c>
       <c r="Y9" t="n">
-        <v>33.68</v>
+        <v>617.7469680170383</v>
       </c>
     </row>
     <row r="10">
@@ -4929,16 +4929,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>767.8440267880003</v>
+        <v>874.4292072760222</v>
       </c>
       <c r="C10" t="n">
-        <v>767.8440267880003</v>
+        <v>1000.431213094458</v>
       </c>
       <c r="D10" t="n">
-        <v>881.1631709130004</v>
+        <v>1000.431213094458</v>
       </c>
       <c r="E10" t="n">
-        <v>881.1631709130004</v>
+        <v>1000.431213094458</v>
       </c>
       <c r="F10" t="n">
         <v>1000.431213094458</v>
@@ -4980,25 +4980,25 @@
         <v>33.68</v>
       </c>
       <c r="S10" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>221.7556791588049</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>221.7556791588049</v>
+        <v>328.3408596468269</v>
       </c>
       <c r="V10" t="n">
-        <v>221.7556791588049</v>
+        <v>328.3408596468269</v>
       </c>
       <c r="W10" t="n">
-        <v>393.6465974184823</v>
+        <v>500.2317779065042</v>
       </c>
       <c r="X10" t="n">
-        <v>544.6773884426758</v>
+        <v>651.2625689306977</v>
       </c>
       <c r="Y10" t="n">
-        <v>656.0866891217081</v>
+        <v>762.67186960973</v>
       </c>
     </row>
     <row r="11">
@@ -5011,19 +5011,19 @@
         <v>1229.164925096351</v>
       </c>
       <c r="C11" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D11" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E11" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F11" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G11" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H11" t="n">
         <v>81.36</v>
@@ -5035,10 +5035,10 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>472.6691130376557</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>690.7012485145707</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="M11" t="n">
         <v>1201.550077243506</v>
@@ -5108,28 +5108,28 @@
         <v>81.36</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>283.4386282495398</v>
       </c>
       <c r="K12" t="n">
-        <v>643.9799167834981</v>
+        <v>695.3814443439232</v>
       </c>
       <c r="L12" t="n">
-        <v>1138.080378378698</v>
+        <v>1189.481905939123</v>
       </c>
       <c r="M12" t="n">
-        <v>1446.910920121557</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N12" t="n">
-        <v>1802.941204729126</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O12" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P12" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q12" t="n">
         <v>2651.414528442776</v>
@@ -5184,34 +5184,34 @@
         <v>193.6715880782802</v>
       </c>
       <c r="H13" t="n">
-        <v>189.862369793817</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="I13" t="n">
-        <v>237.7452487298999</v>
+        <v>241.5544670143631</v>
       </c>
       <c r="J13" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="K13" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="L13" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="M13" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="N13" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="O13" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="P13" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R13" t="n">
         <v>81.36</v>
@@ -5254,40 +5254,40 @@
         <v>815.2116584470142</v>
       </c>
       <c r="E14" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F14" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G14" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H14" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I14" t="n">
         <v>81.36</v>
       </c>
       <c r="J14" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K14" t="n">
-        <v>1182.375479385524</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L14" t="n">
-        <v>2089.404973955146</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M14" t="n">
-        <v>2600.253802684082</v>
+        <v>2208.944689646426</v>
       </c>
       <c r="N14" t="n">
-        <v>3213.474122458845</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="O14" t="n">
-        <v>3213.474122458845</v>
+        <v>3775.207553443145</v>
       </c>
       <c r="P14" t="n">
-        <v>3629.400904947332</v>
+        <v>3775.207553443145</v>
       </c>
       <c r="Q14" t="n">
         <v>4068</v>
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>193.6715880782802</v>
+        <v>137.9063685221783</v>
       </c>
       <c r="C16" t="n">
-        <v>193.6715880782802</v>
+        <v>137.9063685221783</v>
       </c>
       <c r="D16" t="n">
-        <v>193.6715880782802</v>
+        <v>137.9063685221783</v>
       </c>
       <c r="E16" t="n">
-        <v>193.6715880782802</v>
+        <v>81.36</v>
       </c>
       <c r="F16" t="n">
-        <v>193.6715880782802</v>
+        <v>81.36</v>
       </c>
       <c r="G16" t="n">
-        <v>193.6715880782802</v>
+        <v>81.36</v>
       </c>
       <c r="H16" t="n">
-        <v>189.862369793817</v>
+        <v>81.36</v>
       </c>
       <c r="I16" t="n">
-        <v>237.7452487298999</v>
+        <v>129.2428789360829</v>
       </c>
       <c r="J16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="K16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="L16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="M16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="N16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="O16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="P16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="Q16" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="R16" t="n">
-        <v>81.36</v>
+        <v>86.94931630083647</v>
       </c>
       <c r="S16" t="n">
-        <v>81.36</v>
+        <v>86.94931630083647</v>
       </c>
       <c r="T16" t="n">
-        <v>96.18567915880486</v>
+        <v>101.7749954596413</v>
       </c>
       <c r="U16" t="n">
-        <v>169.4868717970915</v>
+        <v>175.076188097928</v>
       </c>
       <c r="V16" t="n">
-        <v>195.0582646830375</v>
+        <v>200.647580983874</v>
       </c>
       <c r="W16" t="n">
-        <v>193.6715880782802</v>
+        <v>200.647580983874</v>
       </c>
       <c r="X16" t="n">
-        <v>193.6715880782802</v>
+        <v>200.647580983874</v>
       </c>
       <c r="Y16" t="n">
-        <v>193.6715880782802</v>
+        <v>200.647580983874</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C17" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D17" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E17" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F17" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G17" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H17" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I17" t="n">
         <v>81.36</v>
       </c>
       <c r="J17" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K17" t="n">
-        <v>1182.375479385524</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L17" t="n">
-        <v>1182.375479385524</v>
+        <v>1129.300343567238</v>
       </c>
       <c r="M17" t="n">
-        <v>1693.224308114459</v>
+        <v>1640.149172296173</v>
       </c>
       <c r="N17" t="n">
-        <v>1814.770397018269</v>
+        <v>2253.369492070936</v>
       </c>
       <c r="O17" t="n">
-        <v>2767.812941040225</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P17" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q17" t="n">
         <v>4068</v>
       </c>
       <c r="R17" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S17" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T17" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U17" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V17" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W17" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X17" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y17" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="18">
@@ -5585,22 +5585,22 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J18" t="n">
-        <v>232.0371006891147</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L18" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M18" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N18" t="n">
-        <v>1802.941204729126</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O18" t="n">
-        <v>2264.733656412845</v>
+        <v>2468.557953866594</v>
       </c>
       <c r="P18" t="n">
         <v>2600.013000882351</v>
@@ -5640,52 +5640,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C19" t="n">
-        <v>193.6715880782802</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="D19" t="n">
-        <v>193.6715880782802</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="E19" t="n">
-        <v>193.6715880782802</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="F19" t="n">
-        <v>193.6715880782802</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="G19" t="n">
-        <v>193.6715880782802</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="H19" t="n">
-        <v>189.862369793817</v>
+        <v>143.0417265520644</v>
       </c>
       <c r="I19" t="n">
-        <v>237.7452487298999</v>
+        <v>190.9246054881473</v>
       </c>
       <c r="J19" t="n">
-        <v>425.5789893823512</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="K19" t="n">
-        <v>425.5789893823512</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="L19" t="n">
-        <v>425.5789893823512</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="M19" t="n">
-        <v>425.5789893823512</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="N19" t="n">
-        <v>425.5789893823512</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="O19" t="n">
-        <v>425.5789893823512</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="P19" t="n">
-        <v>425.5789893823512</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="Q19" t="n">
-        <v>81.36</v>
+        <v>378.7583461405986</v>
       </c>
       <c r="R19" t="n">
         <v>81.36</v>
@@ -5703,13 +5703,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X19" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y19" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="20">
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C20" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D20" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E20" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F20" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G20" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H20" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I20" t="n">
         <v>81.36</v>
@@ -5746,7 +5746,7 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>472.6691130376557</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="L20" t="n">
         <v>690.7012485145707</v>
@@ -5831,16 +5831,16 @@
         <v>1341.904675832448</v>
       </c>
       <c r="M21" t="n">
-        <v>1650.735217575307</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N21" t="n">
-        <v>2006.765502182875</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O21" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P21" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q21" t="n">
         <v>2651.414528442776</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="G22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="H22" t="n">
-        <v>189.862369793817</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="I22" t="n">
-        <v>237.7452487298999</v>
+        <v>242.9411436191204</v>
       </c>
       <c r="J22" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="K22" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="L22" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="M22" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="N22" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="O22" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="P22" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="Q22" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R22" t="n">
         <v>81.36</v>
@@ -5940,13 +5940,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="23">
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C23" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D23" t="n">
         <v>809.6629790963881</v>
@@ -5980,22 +5980,22 @@
         <v>81.36</v>
       </c>
       <c r="J23" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>791.0663663478683</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1698.095860917491</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>2208.944689646426</v>
+        <v>1693.224308114459</v>
       </c>
       <c r="N23" t="n">
-        <v>2822.165009421189</v>
+        <v>2306.444627889222</v>
       </c>
       <c r="O23" t="n">
-        <v>3629.400904947332</v>
+        <v>3259.487171911179</v>
       </c>
       <c r="P23" t="n">
         <v>3629.400904947332</v>
@@ -6025,7 +6025,7 @@
         <v>1777.969718670473</v>
       </c>
       <c r="Y23" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="24">
@@ -6056,25 +6056,25 @@
         <v>81.36</v>
       </c>
       <c r="I24" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J24" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>847.8042142372474</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>1341.904675832448</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M24" t="n">
-        <v>1650.735217575307</v>
+        <v>1642.940339607742</v>
       </c>
       <c r="N24" t="n">
-        <v>2006.765502182875</v>
+        <v>1998.97062421531</v>
       </c>
       <c r="O24" t="n">
-        <v>2468.557953866594</v>
+        <v>2460.763075899029</v>
       </c>
       <c r="P24" t="n">
         <v>2600.013000882351</v>
@@ -6114,52 +6114,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D25" t="n">
-        <v>193.6715880782802</v>
+        <v>133.9105696774259</v>
       </c>
       <c r="E25" t="n">
-        <v>193.6715880782802</v>
+        <v>131.2416726946888</v>
       </c>
       <c r="F25" t="n">
-        <v>193.6715880782802</v>
+        <v>81.36</v>
       </c>
       <c r="G25" t="n">
-        <v>193.6715880782802</v>
+        <v>81.36</v>
       </c>
       <c r="H25" t="n">
-        <v>189.862369793817</v>
+        <v>81.36</v>
       </c>
       <c r="I25" t="n">
-        <v>237.7452487298999</v>
+        <v>129.2428789360829</v>
       </c>
       <c r="J25" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="K25" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="L25" t="n">
-        <v>425.5789893823512</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="M25" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="N25" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="O25" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P25" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R25" t="n">
         <v>81.36</v>
@@ -6177,13 +6177,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="26">
@@ -6193,40 +6193,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C26" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D26" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E26" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F26" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G26" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H26" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I26" t="n">
         <v>81.36</v>
       </c>
       <c r="J26" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>791.0663663478683</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>1698.095860917491</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M26" t="n">
-        <v>1698.095860917491</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N26" t="n">
         <v>1814.770397018269</v>
@@ -6250,19 +6250,19 @@
         <v>3403.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W26" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y26" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6296,16 +6296,16 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>232.0371006891147</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N27" t="n">
         <v>1802.941204729126</v>
@@ -6351,49 +6351,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="C28" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="D28" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="E28" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="F28" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="G28" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="H28" t="n">
-        <v>189.862369793817</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="I28" t="n">
-        <v>237.7452487298999</v>
+        <v>178.4581510048052</v>
       </c>
       <c r="J28" t="n">
-        <v>425.5789893823512</v>
+        <v>366.2918916572565</v>
       </c>
       <c r="K28" t="n">
-        <v>425.5789893823512</v>
+        <v>366.2918916572565</v>
       </c>
       <c r="L28" t="n">
-        <v>425.5789893823512</v>
+        <v>165.738731901924</v>
       </c>
       <c r="M28" t="n">
-        <v>425.5789893823512</v>
+        <v>165.738731901924</v>
       </c>
       <c r="N28" t="n">
-        <v>425.5789893823512</v>
+        <v>165.738731901924</v>
       </c>
       <c r="O28" t="n">
-        <v>425.5789893823512</v>
+        <v>165.738731901924</v>
       </c>
       <c r="P28" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q28" t="n">
         <v>81.36</v>
@@ -6420,7 +6420,7 @@
         <v>193.6715880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
     </row>
     <row r="29">
@@ -6454,13 +6454,13 @@
         <v>81.36</v>
       </c>
       <c r="J29" t="n">
-        <v>294.5205826738834</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>294.5205826738834</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>1201.550077243506</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M29" t="n">
         <v>1201.550077243506</v>
@@ -6481,22 +6481,22 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W29" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X29" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y29" t="n">
         <v>1483.211511357417</v>
@@ -6530,16 +6530,16 @@
         <v>81.36</v>
       </c>
       <c r="I30" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J30" t="n">
-        <v>232.0371006891147</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>643.9799167834981</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L30" t="n">
-        <v>1138.080378378698</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M30" t="n">
         <v>1446.910920121557</v>
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="C31" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="D31" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="E31" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="F31" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="G31" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="H31" t="n">
-        <v>189.862369793817</v>
+        <v>128.1527303890163</v>
       </c>
       <c r="I31" t="n">
-        <v>237.7452487298999</v>
+        <v>176.0356093250992</v>
       </c>
       <c r="J31" t="n">
-        <v>425.5789893823512</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="K31" t="n">
-        <v>425.5789893823512</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="L31" t="n">
-        <v>425.5789893823512</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="M31" t="n">
-        <v>425.5789893823512</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="N31" t="n">
-        <v>425.5789893823512</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="O31" t="n">
-        <v>425.5789893823512</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="P31" t="n">
-        <v>81.36</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="Q31" t="n">
-        <v>81.36</v>
+        <v>363.8693499775505</v>
       </c>
       <c r="R31" t="n">
         <v>81.36</v>
@@ -6651,13 +6651,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y31" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
     </row>
     <row r="32">
@@ -6667,16 +6667,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C32" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D32" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E32" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F32" t="n">
         <v>446.7812434247916</v>
@@ -6691,52 +6691,52 @@
         <v>81.36</v>
       </c>
       <c r="J32" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K32" t="n">
-        <v>472.6691130376557</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L32" t="n">
-        <v>690.7012485145707</v>
+        <v>1129.300343567238</v>
       </c>
       <c r="M32" t="n">
-        <v>1201.550077243506</v>
+        <v>1640.149172296173</v>
       </c>
       <c r="N32" t="n">
-        <v>1814.770397018269</v>
+        <v>2253.369492070936</v>
       </c>
       <c r="O32" t="n">
-        <v>2767.812941040225</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P32" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q32" t="n">
         <v>4068</v>
       </c>
       <c r="R32" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S32" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T32" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U32" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V32" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W32" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X32" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y32" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="33">
@@ -6770,10 +6770,10 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>232.0371006891147</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L33" t="n">
         <v>1138.080378378698</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F34" t="n">
-        <v>193.6715880782802</v>
+        <v>145.1765919883486</v>
       </c>
       <c r="G34" t="n">
-        <v>193.6715880782802</v>
+        <v>145.1765919883486</v>
       </c>
       <c r="H34" t="n">
-        <v>189.862369793817</v>
+        <v>145.1765919883486</v>
       </c>
       <c r="I34" t="n">
-        <v>237.7452487298999</v>
+        <v>193.0594709244315</v>
       </c>
       <c r="J34" t="n">
-        <v>425.5789893823512</v>
+        <v>380.8932115768829</v>
       </c>
       <c r="K34" t="n">
-        <v>425.5789893823512</v>
+        <v>380.8932115768829</v>
       </c>
       <c r="L34" t="n">
-        <v>425.5789893823512</v>
+        <v>380.8932115768829</v>
       </c>
       <c r="M34" t="n">
-        <v>425.5789893823512</v>
+        <v>380.8932115768829</v>
       </c>
       <c r="N34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="O34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6888,13 +6888,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="35">
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G35" t="n">
         <v>103.3156148520479</v>
@@ -6937,10 +6937,10 @@
         <v>436.0291130376557</v>
       </c>
       <c r="M35" t="n">
-        <v>946.8779417665908</v>
+        <v>436.0291130376558</v>
       </c>
       <c r="N35" t="n">
-        <v>1243.990904947333</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O35" t="n">
         <v>1243.990904947333</v>
@@ -6952,28 +6952,28 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D36" t="n">
         <v>44.72</v>
@@ -7034,25 +7034,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="37">
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
@@ -7174,16 +7174,16 @@
         <v>989.4391130376558</v>
       </c>
       <c r="M38" t="n">
-        <v>1500.287941766591</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N38" t="n">
-        <v>1682.59</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O38" t="n">
-        <v>2236</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="P38" t="n">
-        <v>2236</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7204,13 +7204,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
         <v>44.72</v>
@@ -7271,25 +7271,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="40">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
         <v>946.5478354584615</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7396,7 +7396,7 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
@@ -7405,22 +7405,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L41" t="n">
         <v>989.4391130376558</v>
       </c>
       <c r="M41" t="n">
-        <v>989.4391130376558</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N41" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O41" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7460,16 +7460,16 @@
         <v>119.2429040110725</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="G42" t="n">
         <v>44.72</v>
@@ -7514,7 +7514,7 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
         <v>357.8124310491301</v>
@@ -7639,19 +7639,19 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M44" t="n">
+        <v>946.8779417665908</v>
+      </c>
+      <c r="N44" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
         <v>1797.400904947332</v>
@@ -7745,22 +7745,22 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U45" t="n">
-        <v>359.6638499037541</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V45" t="n">
-        <v>294.5015598113094</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y45" t="n">
         <v>90.8376455473191</v>
@@ -7827,16 +7827,16 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X46" t="n">
         <v>745.8791912947012</v>
@@ -7976,16 +7976,16 @@
         <v>965.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>898.2489580698352</v>
+        <v>485.9771267186678</v>
       </c>
       <c r="O2" t="n">
         <v>491.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>9.015228689513952</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.8226843274854</v>
+        <v>593.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,10 +8210,10 @@
         <v>421.0000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>948.2520266322163</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>70.24786957409245</v>
@@ -8222,7 +8222,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>593.8226843274854</v>
+        <v>576.8125833173842</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>965.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>491.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406814136</v>
+        <v>421.2870600406814</v>
       </c>
       <c r="Q8" t="n">
-        <v>576.8125833173845</v>
+        <v>181.5508529763179</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,13 +8678,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>220.2344802797121</v>
+        <v>19.36828066462772</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
@@ -8927,13 +8927,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P14" t="n">
-        <v>420.4151231603661</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>468.5726303445106</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>341.6504820397674</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>600.0227852454004</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
         <v>1032.917105959907</v>
@@ -9170,7 +9170,7 @@
         <v>870.5779326741233</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,10 +9389,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="L20" t="n">
-        <v>220.2344802797121</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,10 +9638,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>885.6376630348439</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>373.9372954307356</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>595.102024838298</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
         <v>1032.917105959907</v>
@@ -10097,16 +10097,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>250.3567261176999</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
@@ -10334,13 +10334,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>220.2344802797121</v>
+        <v>341.6504820397674</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10355,7 +10355,7 @@
         <v>870.5779326741233</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,13 +10580,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>777.3630622928068</v>
+        <v>734.371980200822</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
         <v>559.2870600406815</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
         <v>629.2478695740924</v>
@@ -10829,7 +10829,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>172.8226843274854</v>
+        <v>313.9750954005603</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,16 +11048,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>559</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>801.385149773304</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
         <v>629.2478695740924</v>
@@ -11066,7 +11066,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>313.9750954005603</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>777.3630622928068</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -23399,7 +23399,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23423,13 +23423,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>462.4478973282775</v>
+        <v>117.8999717381312</v>
       </c>
       <c r="Q13" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>47.72524664804467</v>
@@ -23627,7 +23627,7 @@
         <v>60.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>49.38285596774193</v>
@@ -23636,7 +23636,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23666,7 +23666,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>160.8253284926234</v>
+        <v>273.7760977263302</v>
       </c>
       <c r="S16" t="n">
         <v>137.3734797028554</v>
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X16" t="n">
         <v>22.44364543010755</v>
@@ -23858,7 +23858,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>60.53621805555548</v>
@@ -23900,10 +23900,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>501.6021279811511</v>
+        <v>207.1777653019584</v>
       </c>
       <c r="S19" t="n">
         <v>137.3734797028554</v>
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X19" t="n">
         <v>22.44364543010755</v>
@@ -24110,7 +24110,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -24137,10 +24137,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>500.839266425598</v>
+        <v>154.918530996742</v>
       </c>
       <c r="R22" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>137.3734797028554</v>
@@ -24155,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X22" t="n">
         <v>22.44364543010755</v>
@@ -24335,19 +24335,19 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D25" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>55.98090483695654</v>
+        <v>53.33869682404687</v>
       </c>
       <c r="F25" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>20.04387284153003</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -24362,7 +24362,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>295.6316114025499</v>
+        <v>62.27215800990101</v>
       </c>
       <c r="N25" t="n">
         <v>346.1850752716849</v>
@@ -24377,7 +24377,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>137.3734797028554</v>
@@ -24392,7 +24392,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X25" t="n">
         <v>22.44364543010755</v>
@@ -24584,7 +24584,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>295.6316114025499</v>
@@ -24608,10 +24608,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>462.4478973282775</v>
+        <v>378.9129527453727</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
@@ -24635,7 +24635,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24845,13 +24845,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>501.6021279811511</v>
+        <v>221.917871503376</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24866,13 +24866,13 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -25052,13 +25052,13 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F34" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>20.04387284153003</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25076,7 +25076,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>346.1850752716849</v>
+        <v>49.64719581057085</v>
       </c>
       <c r="O34" t="n">
         <v>415.445564079015</v>
@@ -25088,7 +25088,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X34" t="n">
         <v>22.44364543010755</v>
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5316580.200168882</v>
+        <v>5316580.200168881</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6326635.910610374</v>
+        <v>6326635.910610373</v>
       </c>
     </row>
     <row r="8">
@@ -26284,22 +26284,22 @@
         <v>1069470.75223217</v>
       </c>
       <c r="G2" t="n">
+        <v>1069470.752232171</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1069470.752232171</v>
+      </c>
+      <c r="I2" t="n">
         <v>1069470.75223217</v>
       </c>
-      <c r="H2" t="n">
-        <v>1069470.75223217</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1069470.752232171</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1069470.75223217</v>
       </c>
       <c r="K2" t="n">
         <v>1069470.75223217</v>
       </c>
       <c r="L2" t="n">
-        <v>1069470.75223217</v>
+        <v>1069470.752232171</v>
       </c>
       <c r="M2" t="n">
         <v>1133439.336299335</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789646</v>
+        <v>565885.0565724099</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743711</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482317</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.2900507811</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121191</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696402</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464519</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476347</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>359667.9770568254</v>
+        <v>358105.3639633803</v>
       </c>
       <c r="C6" t="n">
-        <v>509892.4928203705</v>
+        <v>508329.8797269252</v>
       </c>
       <c r="D6" t="n">
-        <v>511927.765818409</v>
+        <v>510365.152724964</v>
       </c>
       <c r="E6" t="n">
-        <v>153076.9377203085</v>
+        <v>150740.2298086111</v>
       </c>
       <c r="F6" t="n">
-        <v>544322.488483938</v>
+        <v>541985.7805722406</v>
       </c>
       <c r="G6" t="n">
-        <v>545778.0450930865</v>
+        <v>543441.3371813896</v>
       </c>
       <c r="H6" t="n">
-        <v>547235.6219317489</v>
+        <v>544898.9140200515</v>
       </c>
       <c r="I6" t="n">
-        <v>548695.2335713354</v>
+        <v>546358.5256596376</v>
       </c>
       <c r="J6" t="n">
-        <v>221964.8947742273</v>
+        <v>219628.1868625304</v>
       </c>
       <c r="K6" t="n">
-        <v>551620.620497416</v>
+        <v>549283.9125857186</v>
       </c>
       <c r="L6" t="n">
-        <v>553086.4258962329</v>
+        <v>550749.717984536</v>
       </c>
       <c r="M6" t="n">
-        <v>393977.2617572342</v>
+        <v>392235.4119441262</v>
       </c>
       <c r="N6" t="n">
-        <v>544518.1587920879</v>
+        <v>542776.3089789799</v>
       </c>
       <c r="O6" t="n">
-        <v>366485.898049826</v>
+        <v>364744.0482367182</v>
       </c>
       <c r="P6" t="n">
-        <v>548456.5009008361</v>
+        <v>546714.6510877283</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>225</v>
@@ -27008,7 +27008,7 @@
         <v>125</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>225</v>
@@ -27024,11 +27024,11 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
@@ -27042,7 +27042,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -27057,7 +27057,7 @@
         <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>138</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>223.0898107180206</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27530,7 +27530,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>207.3202110067391</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27594,16 +27594,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>339.8716458549032</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
@@ -27612,13 +27612,13 @@
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>194.2206408133782</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>82.46360744287983</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27736,7 +27736,7 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27752,22 +27752,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>185.682627621886</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>139.8182410159027</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27831,7 +27831,7 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27843,7 +27843,7 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>35.95412362508684</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>345.9482232840736</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27967,7 +27967,7 @@
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,22 +28034,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>126.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>389.0798434146775</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>293.5799390439246</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28068,16 +28068,16 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>394.8556258480022</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>220.9936694500629</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28147,7 +28147,7 @@
         <v>225</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="D11" t="n">
         <v>225</v>
@@ -28162,7 +28162,7 @@
         <v>225</v>
       </c>
       <c r="H11" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="I11" t="n">
         <v>150.0811596826846</v>
@@ -28244,13 +28244,13 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>78.91122027701098</v>
       </c>
       <c r="K12" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28268,7 +28268,7 @@
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28390,7 +28390,7 @@
         <v>225</v>
       </c>
       <c r="E14" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="F14" t="n">
         <v>225</v>
@@ -28402,7 +28402,7 @@
         <v>225</v>
       </c>
       <c r="I14" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28639,7 +28639,7 @@
         <v>225</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S17" t="n">
         <v>225</v>
@@ -28721,7 +28721,7 @@
         <v>225</v>
       </c>
       <c r="J18" t="n">
-        <v>19.11687125883914</v>
+        <v>225</v>
       </c>
       <c r="K18" t="n">
         <v>225</v>
@@ -28739,7 +28739,7 @@
         <v>225</v>
       </c>
       <c r="P18" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q18" t="n">
         <v>225</v>
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="C20" t="n">
         <v>225</v>
@@ -28876,7 +28876,7 @@
         <v>225</v>
       </c>
       <c r="I20" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28967,19 +28967,19 @@
         <v>225</v>
       </c>
       <c r="M21" t="n">
-        <v>225</v>
+        <v>71.03760616835939</v>
       </c>
       <c r="N21" t="n">
         <v>225</v>
       </c>
       <c r="O21" t="n">
-        <v>19.11687125883898</v>
+        <v>225</v>
       </c>
       <c r="P21" t="n">
         <v>225</v>
       </c>
       <c r="Q21" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>225</v>
@@ -29098,7 +29098,7 @@
         <v>225</v>
       </c>
       <c r="D23" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="E23" t="n">
         <v>225</v>
@@ -29161,7 +29161,7 @@
         <v>225</v>
       </c>
       <c r="Y23" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24">
@@ -29192,7 +29192,7 @@
         <v>225</v>
       </c>
       <c r="I24" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>225</v>
@@ -29213,7 +29213,7 @@
         <v>225</v>
       </c>
       <c r="P24" t="n">
-        <v>19.11687125883908</v>
+        <v>26.99048536749045</v>
       </c>
       <c r="Q24" t="n">
         <v>225</v>
@@ -29350,7 +29350,7 @@
         <v>225</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29386,7 +29386,7 @@
         <v>225</v>
       </c>
       <c r="U26" t="n">
-        <v>219.50680744288</v>
+        <v>225</v>
       </c>
       <c r="V26" t="n">
         <v>225</v>
@@ -29432,7 +29432,7 @@
         <v>225</v>
       </c>
       <c r="J27" t="n">
-        <v>19.11687125883914</v>
+        <v>225</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
@@ -29444,7 +29444,7 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O27" t="n">
         <v>225</v>
@@ -29617,7 +29617,7 @@
         <v>225</v>
       </c>
       <c r="S29" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="T29" t="n">
         <v>225</v>
@@ -29635,7 +29635,7 @@
         <v>225</v>
       </c>
       <c r="Y29" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
     </row>
     <row r="30">
@@ -29666,10 +29666,10 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
-        <v>19.11687125883914</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29678,7 +29678,7 @@
         <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>225</v>
+        <v>26.99048536749062</v>
       </c>
       <c r="N30" t="n">
         <v>225</v>
@@ -29815,7 +29815,7 @@
         <v>225</v>
       </c>
       <c r="F32" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="G32" t="n">
         <v>225</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S32" t="n">
         <v>225</v>
@@ -29906,13 +29906,13 @@
         <v>225</v>
       </c>
       <c r="J33" t="n">
-        <v>19.11687125883914</v>
+        <v>225</v>
       </c>
       <c r="K33" t="n">
         <v>225</v>
       </c>
       <c r="L33" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M33" t="n">
         <v>225</v>
@@ -30055,7 +30055,7 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30119,13 +30119,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>350</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30170,10 +30170,10 @@
         <v>350</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T36" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="U36" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30340,7 +30340,7 @@
         <v>350</v>
       </c>
       <c r="W38" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X38" t="n">
         <v>350</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
         <v>350</v>
-      </c>
-      <c r="C39" t="n">
-        <v>269.4903246609786</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30374,7 +30374,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30407,7 +30407,7 @@
         <v>350</v>
       </c>
       <c r="S39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="T39" t="n">
         <v>350</v>
@@ -30438,7 +30438,7 @@
         <v>350</v>
       </c>
       <c r="C40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="D40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30532,10 +30532,10 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30596,7 +30596,7 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
@@ -30608,7 +30608,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>263.0617733495849</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
@@ -30650,10 +30650,10 @@
         <v>350</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>350</v>
@@ -30881,13 +30881,13 @@
         <v>350</v>
       </c>
       <c r="S45" t="n">
+        <v>287.3222374745575</v>
+      </c>
+      <c r="T45" t="n">
         <v>350</v>
       </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
       <c r="U45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V45" t="n">
         <v>350</v>
@@ -30899,7 +30899,7 @@
         <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -30975,7 +30975,7 @@
         <v>350</v>
       </c>
       <c r="X46" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y46" t="n">
         <v>350</v>
@@ -34755,16 +34755,16 @@
         <v>421</v>
       </c>
       <c r="N2" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="O2" t="n">
         <v>421</v>
       </c>
       <c r="P2" t="n">
-        <v>8.728168648832536</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,16 +34880,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>58.89074101794667</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
@@ -34898,13 +34898,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>17.58718519325988</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34989,10 +34989,10 @@
         <v>421.0000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>403.9898989898989</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>421</v>
+        <v>403.9898989898988</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,7 +35117,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35129,7 +35129,7 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35138,7 +35138,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6851747891790761</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>111.479226198857</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>146.7779130678574</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>421</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>421</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
       <c r="Q8" t="n">
-        <v>403.989898989899</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35354,16 +35354,16 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>120.4727698802602</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>70.03527817560494</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35457,13 +35457,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
-        <v>220.2344802797121</v>
+        <v>19.36828066462772</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>619.4144644189528</v>
@@ -35530,13 +35530,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>204.1198265146867</v>
       </c>
       <c r="K12" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35554,7 +35554,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35691,10 +35691,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L14" t="n">
         <v>916.1914086561842</v>
@@ -35706,13 +35706,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P14" t="n">
-        <v>420.1280631196846</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>295.7499460170251</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>341.6504820397674</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>122.7738271755652</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
         <v>962.6692363858147</v>
@@ -35949,7 +35949,7 @@
         <v>870.2908726334418</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,7 +36007,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J18" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>416.1038546407913</v>
@@ -36025,7 +36025,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q18" t="n">
         <v>51.92073490952041</v>
@@ -36168,10 +36168,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="L20" t="n">
-        <v>220.2344802797121</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36253,19 +36253,19 @@
         <v>499.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>311.9500421645043</v>
+        <v>157.9876483328637</v>
       </c>
       <c r="N21" t="n">
         <v>359.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>260.5738931615854</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P21" t="n">
         <v>338.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,10 +36417,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>815.3897934607513</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>373.6502353900542</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>350.2086062376757</v>
@@ -36499,7 +36499,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>132.7828757734923</v>
+        <v>140.6564898821437</v>
       </c>
       <c r="Q24" t="n">
         <v>51.92073490952041</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>117.8530667684628</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
         <v>962.6692363858147</v>
@@ -36718,7 +36718,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
@@ -36730,7 +36730,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O27" t="n">
         <v>466.4570219027464</v>
@@ -36876,16 +36876,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>215.3137198726095</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
@@ -36952,10 +36952,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36964,7 +36964,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M30" t="n">
-        <v>311.9500421645043</v>
+        <v>113.9405275319949</v>
       </c>
       <c r="N30" t="n">
         <v>359.6265501086548</v>
@@ -37113,13 +37113,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L32" t="n">
-        <v>220.2344802797121</v>
+        <v>341.6504820397674</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
@@ -37134,7 +37134,7 @@
         <v>870.2908726334418</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,13 +37192,13 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>416.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M33" t="n">
         <v>311.9500421645043</v>
@@ -37359,13 +37359,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>300.1141042229716</v>
+        <v>257.1230221309867</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P35" t="n">
         <v>559</v>
@@ -37596,10 +37596,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
         <v>559</v>
@@ -37608,7 +37608,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>141.1524110730749</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37724,7 +37724,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608951</v>
       </c>
       <c r="D40" t="n">
         <v>64.46378194444452</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37827,16 +37827,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>559</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>257.1230221309867</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>559</v>
@@ -37845,7 +37845,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>141.1524110730749</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
+        <v>300.1141042229716</v>
+      </c>
+      <c r="O44" t="n">
         <v>559</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
@@ -38261,7 +38261,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y46" t="n">
         <v>62.53464715053764</v>
